--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
@@ -734,7 +734,7 @@
         <v>600</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="N2" t="s">
         <v>47</v>
@@ -743,7 +743,7 @@
         <v>48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.01572817524315</v>
+        <v>0.997945522737853</v>
       </c>
       <c r="Q2" t="n">
         <v>0.999026524050469</v>
@@ -755,7 +755,7 @@
         <v>2.89323191492191</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="U2" t="n">
         <v>0.999769549580697</v>
@@ -773,16 +773,16 @@
         <v>149</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3359293631417</v>
+        <v>2.29503355936848</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000633902133824072</v>
+        <v>0.00062280422235237</v>
       </c>
       <c r="AB2" t="n">
         <v>1.10869208822785</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0314898091802709</v>
+        <v>0.0309385078107122</v>
       </c>
       <c r="AD2" t="s">
         <v>47</v>
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0272394087536914</v>
+        <v>0.0267625203970198</v>
       </c>
       <c r="AG2" t="n">
         <v>0.665073921237439</v>
@@ -803,7 +803,7 @@
         <v>1.76089172033418</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0314898091802709</v>
+        <v>0.0309385078107122</v>
       </c>
       <c r="AK2" t="n">
         <v>0.665931303103025</v>
@@ -821,10 +821,10 @@
         <v>149</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.3359293631417</v>
+        <v>2.29503355936848</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0044373149367685</v>
+        <v>0.00435962955646659</v>
       </c>
       <c r="AR2" t="n">
         <v>1.15603864478166</v>
@@ -866,7 +866,7 @@
         <v>900</v>
       </c>
       <c r="M3" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="N3" t="s">
         <v>47</v>
@@ -875,7 +875,7 @@
         <v>48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.10063846684457</v>
+        <v>1.08136926484062</v>
       </c>
       <c r="Q3" t="n">
         <v>0.998731607593589</v>
@@ -887,7 +887,7 @@
         <v>4.6166245421767</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="U3" t="n">
         <v>0.9999173464781</v>
@@ -905,16 +905,16 @@
         <v>192</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.33605629372157</v>
+        <v>2.29515826773728</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000491801324994015</v>
+        <v>0.00048319121426048</v>
       </c>
       <c r="AB3" t="n">
         <v>1.13932484045474</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0765684447151247</v>
+        <v>0.0752279383883071</v>
       </c>
       <c r="AD3" t="s">
         <v>47</v>
@@ -923,7 +923,7 @@
         <v>51</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0760943600684935</v>
+        <v>0.0747621536813002</v>
       </c>
       <c r="AG3" t="n">
         <v>0.970695174412968</v>
@@ -935,7 +935,7 @@
         <v>1.55605584008292</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0765684447151247</v>
+        <v>0.0752279383883071</v>
       </c>
       <c r="AK3" t="n">
         <v>0.97052787072339</v>
@@ -953,10 +953,10 @@
         <v>192</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33605629372157</v>
+        <v>2.29515826773728</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0034426092749581</v>
+        <v>0.00338233849982336</v>
       </c>
       <c r="AR3" t="n">
         <v>1.00623022056043</v>
@@ -998,7 +998,7 @@
         <v>600</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="N4" t="s">
         <v>47</v>
@@ -1007,7 +1007,7 @@
         <v>48</v>
       </c>
       <c r="P4" t="n">
-        <v>0.932800122520638</v>
+        <v>0.916469315873757</v>
       </c>
       <c r="Q4" t="n">
         <v>0.998014485619764</v>
@@ -1019,7 +1019,7 @@
         <v>4.23502656211206</v>
       </c>
       <c r="T4" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="U4" t="n">
         <v>0.999860422432155</v>
@@ -1037,16 +1037,16 @@
         <v>166</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.33411295450244</v>
+        <v>2.29324895113058</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000567910694526141</v>
+        <v>0.00055796811463031</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17747149778095</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0337112943119567</v>
+        <v>0.0331211007475123</v>
       </c>
       <c r="AD4" t="s">
         <v>47</v>
@@ -1055,7 +1055,7 @@
         <v>51</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0336412225079778</v>
+        <v>0.0330522557112562</v>
       </c>
       <c r="AG4" t="n">
         <v>0.859726359528916</v>
@@ -1067,7 +1067,7 @@
         <v>1.38250632850401</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0337112943119567</v>
+        <v>0.0331211007475123</v>
       </c>
       <c r="AK4" t="n">
         <v>0.859492457974167</v>
@@ -1085,10 +1085,10 @@
         <v>166</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.33411295450244</v>
+        <v>2.29324895113058</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00397537486168299</v>
+        <v>0.00390577680241217</v>
       </c>
       <c r="AR4" t="n">
         <v>1.00208291491079</v>
@@ -1132,7 +1132,7 @@
         <v>600</v>
       </c>
       <c r="M5" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="N5" t="s">
         <v>47</v>
@@ -1141,7 +1141,7 @@
         <v>51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.30314854895781</v>
+        <v>1.28033394326534</v>
       </c>
       <c r="Q5" t="n">
         <v>0.999791962695814</v>
@@ -1153,7 +1153,7 @@
         <v>0.710998752972665</v>
       </c>
       <c r="T5" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="U5" t="n">
         <v>0.999795764899988</v>
@@ -1171,16 +1171,16 @@
         <v>62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.33394904079873</v>
+        <v>2.29308790711238</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00153549278999916</v>
+        <v>0.00150861046520551</v>
       </c>
       <c r="AB5" t="n">
         <v>1.01589978521503</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.353678991732009</v>
+        <v>0.347487029392391</v>
       </c>
       <c r="AD5" t="s">
         <v>47</v>
@@ -1189,7 +1189,7 @@
         <v>51</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.330400946519775</v>
+        <v>0.324616519777869</v>
       </c>
       <c r="AG5" t="n">
         <v>0.99007467292149</v>
@@ -1201,7 +1201,7 @@
         <v>1.25113422504825</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.353678991732009</v>
+        <v>0.347487029392391</v>
       </c>
       <c r="AK5" t="n">
         <v>0.990407805013714</v>
@@ -1219,10 +1219,10 @@
         <v>62</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.33394904079873</v>
+        <v>2.29308790711238</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0107484495299941</v>
+        <v>0.0105602732564386</v>
       </c>
       <c r="AR5" t="n">
         <v>1.07045393016403</v>
@@ -1260,7 +1260,7 @@
         <v>600</v>
       </c>
       <c r="M6" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="N6" t="s">
         <v>47</v>
@@ -1269,7 +1269,7 @@
         <v>48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.31933987276378</v>
+        <v>1.29624180079376</v>
       </c>
       <c r="Q6" t="n">
         <v>0.999887278397298</v>
@@ -1281,7 +1281,7 @@
         <v>1.003946291558</v>
       </c>
       <c r="T6" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="U6" t="n">
         <v>0.999894443336438</v>
@@ -1299,16 +1299,16 @@
         <v>117</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3331479824422</v>
+        <v>2.29230087312057</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000807317640983459</v>
+        <v>0.000793183693121306</v>
       </c>
       <c r="AB6" t="n">
         <v>1.0164644481466</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.396629714787707</v>
+        <v>0.389685801481711</v>
       </c>
       <c r="AD6" t="s">
         <v>47</v>
@@ -1317,7 +1317,7 @@
         <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.369704402424142</v>
+        <v>0.36323187849675</v>
       </c>
       <c r="AG6" t="n">
         <v>0.997780915269485</v>
@@ -1329,7 +1329,7 @@
         <v>1.24952730832149</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.396629714787707</v>
+        <v>0.389685801481711</v>
       </c>
       <c r="AK6" t="n">
         <v>0.998122550225431</v>
@@ -1347,10 +1347,10 @@
         <v>117</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.3331479824422</v>
+        <v>2.29230087312057</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00565122348688421</v>
+        <v>0.00555228585184914</v>
       </c>
       <c r="AR6" t="n">
         <v>1.07282929872356</v>
@@ -1392,7 +1392,7 @@
         <v>300</v>
       </c>
       <c r="M7" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="N7" t="s">
         <v>47</v>
@@ -1401,7 +1401,7 @@
         <v>48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.12550151487279</v>
+        <v>1.10579702815972</v>
       </c>
       <c r="Q7" t="n">
         <v>0.997341812842276</v>
@@ -1413,7 +1413,7 @@
         <v>2.44875624758245</v>
       </c>
       <c r="T7" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="U7" t="n">
         <v>0.997707251307285</v>
@@ -1431,16 +1431,16 @@
         <v>69</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.33232743441018</v>
+        <v>2.29149469066478</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0013760043860827</v>
+        <v>0.00135191427177863</v>
       </c>
       <c r="AB7" t="n">
         <v>1.07367388439862</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0384520122066485</v>
+        <v>0.0377788214969031</v>
       </c>
       <c r="AD7" t="s">
         <v>47</v>
@@ -1449,7 +1449,7 @@
         <v>51</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0384203355769582</v>
+        <v>0.0377476994393041</v>
       </c>
       <c r="AG7" t="n">
         <v>0.497133148131768</v>
@@ -1461,7 +1461,7 @@
         <v>1.61652391538232</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0384520122066485</v>
+        <v>0.0377788214969031</v>
       </c>
       <c r="AK7" t="n">
         <v>0.496975719496566</v>
@@ -1479,10 +1479,10 @@
         <v>69</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.33232743441018</v>
+        <v>2.29149469066478</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00963203070257893</v>
+        <v>0.00946339990245041</v>
       </c>
       <c r="AR7" t="n">
         <v>1.00082447561206</v>
@@ -1524,7 +1524,7 @@
         <v>300</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="N8" t="s">
         <v>47</v>
@@ -1533,7 +1533,7 @@
         <v>48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.27234696475888</v>
+        <v>1.2500716114784</v>
       </c>
       <c r="Q8" t="n">
         <v>0.999633472356177</v>
@@ -1545,7 +1545,7 @@
         <v>1.1474396140762</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="U8" t="n">
         <v>0.99977497116895</v>
@@ -1563,16 +1563,16 @@
         <v>77</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.33000905473764</v>
+        <v>2.2892168995484</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001229556229413</v>
+        <v>0.00120803002614691</v>
       </c>
       <c r="AB8" t="n">
         <v>1.04592823501308</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.046013949999614</v>
+        <v>0.0452083702163778</v>
       </c>
       <c r="AD8" t="s">
         <v>47</v>
@@ -1581,7 +1581,7 @@
         <v>51</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0387741109187982</v>
+        <v>0.0380952811319747</v>
       </c>
       <c r="AG8" t="n">
         <v>0.693680686527493</v>
@@ -1593,7 +1593,7 @@
         <v>1.20999491759047</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.046013949999614</v>
+        <v>0.0452083702163778</v>
       </c>
       <c r="AK8" t="n">
         <v>0.695258815852541</v>
@@ -1611,10 +1611,10 @@
         <v>77</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33000905473764</v>
+        <v>2.2892168995484</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00860689360589101</v>
+        <v>0.00845621018302839</v>
       </c>
       <c r="AR8" t="n">
         <v>1.18671837752715</v>
@@ -1654,7 +1654,7 @@
         <v>300</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="N9" t="s">
         <v>47</v>
@@ -1663,7 +1663,7 @@
         <v>48</v>
       </c>
       <c r="P9" t="n">
-        <v>1.09028443267916</v>
+        <v>1.07119650180274</v>
       </c>
       <c r="Q9" t="n">
         <v>0.998592889197321</v>
@@ -1675,7 +1675,7 @@
         <v>1.1975836661462</v>
       </c>
       <c r="T9" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="U9" t="n">
         <v>0.998747896186046</v>
@@ -1693,16 +1693,16 @@
         <v>48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.32973961803961</v>
+        <v>2.28895217995805</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00198275712173584</v>
+        <v>0.00194804440847494</v>
       </c>
       <c r="AB9" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00484885854885949</v>
+        <v>-0.00476396815325628</v>
       </c>
       <c r="AD9" t="s">
         <v>47</v>
@@ -1711,7 +1711,7 @@
         <v>67</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00403629265498706</v>
+        <v>-0.00396562808995602</v>
       </c>
       <c r="AG9" t="n">
         <v>-0.016477614613488</v>
@@ -1723,7 +1723,7 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.00484885854885949</v>
+        <v>-0.00476396815325628</v>
       </c>
       <c r="AK9" t="n">
         <v>-0.0160211732658191</v>
@@ -1741,10 +1741,10 @@
         <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.32973961803961</v>
+        <v>2.28895217995805</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0138792998521509</v>
+        <v>0.0136363108593246</v>
       </c>
       <c r="AR9" t="n">
         <v>1.20131491032209</v>
@@ -1780,7 +1780,7 @@
         <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="N10" t="s">
         <v>47</v>
@@ -1789,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26070021803685</v>
+        <v>1.2386287677836</v>
       </c>
       <c r="Q10" t="n">
         <v>0.999713524615498</v>
@@ -1801,7 +1801,7 @@
         <v>1.7955954188882</v>
       </c>
       <c r="T10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="U10" t="n">
         <v>0.999884540341955</v>
@@ -1819,16 +1819,16 @@
         <v>70</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.32526764396137</v>
+        <v>2.28455849804792</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.000814454516273686</v>
+        <v>0.000800195621032545</v>
       </c>
       <c r="AB10" t="n">
         <v>1.06371077614318</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00965562852738834</v>
+        <v>0.00948658459318646</v>
       </c>
       <c r="AD10" t="s">
         <v>47</v>
@@ -1837,7 +1837,7 @@
         <v>51</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00966301603762399</v>
+        <v>0.00949384276810327</v>
       </c>
       <c r="AG10" t="n">
         <v>0.030518900730106</v>
@@ -1849,7 +1849,7 @@
         <v>3.79189154513842</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.00965562852738834</v>
+        <v>0.00948658459318646</v>
       </c>
       <c r="AK10" t="n">
         <v>0.0305018423219471</v>
@@ -1867,10 +1867,10 @@
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.32526764396137</v>
+        <v>2.28455849804792</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0057011816139158</v>
+        <v>0.00560136934722782</v>
       </c>
       <c r="AR10" t="n">
         <v>0.999235486083549</v>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
@@ -218,10 +218,10 @@
     <t xml:space="preserve">AICc | MDF</t>
   </si>
   <si>
-    <t xml:space="preserve">MDF (LM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDF (HM)</t>
+    <t xml:space="preserve">Noise (LM.MAE) | MDF (LM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noise (HM.MAE) | MDF (HM)</t>
   </si>
   <si>
     <t xml:space="preserve">YMF_Seam</t>
@@ -734,7 +734,7 @@
         <v>600</v>
       </c>
       <c r="M2" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="N2" t="s">
         <v>47</v>
@@ -743,7 +743,7 @@
         <v>48</v>
       </c>
       <c r="P2" t="n">
-        <v>0.997945522737853</v>
+        <v>0.989737444125356</v>
       </c>
       <c r="Q2" t="n">
         <v>0.999026524050469</v>
@@ -755,7 +755,7 @@
         <v>2.89323191492191</v>
       </c>
       <c r="T2" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="U2" t="n">
         <v>0.999769549580697</v>
@@ -773,16 +773,16 @@
         <v>149</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.29503355936848</v>
+        <v>2.2761569619547</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00062280422235237</v>
+        <v>0.00108094292630142</v>
       </c>
       <c r="AB2" t="n">
         <v>1.10869208822785</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0309385078107122</v>
+        <v>0.0306840393066931</v>
       </c>
       <c r="AD2" t="s">
         <v>47</v>
@@ -791,7 +791,7 @@
         <v>51</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0267625203970198</v>
+        <v>0.0265423992919272</v>
       </c>
       <c r="AG2" t="n">
         <v>0.665073921237439</v>
@@ -803,7 +803,7 @@
         <v>1.76089172033418</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0309385078107122</v>
+        <v>0.0306840393066931</v>
       </c>
       <c r="AK2" t="n">
         <v>0.665931303103025</v>
@@ -812,19 +812,19 @@
         <v>1.75863641061905</v>
       </c>
       <c r="AM2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO2" t="n">
         <v>149</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.29503355936848</v>
+        <v>2.2761569619547</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00435962955646659</v>
+        <v>0.00277956752477507</v>
       </c>
       <c r="AR2" t="n">
         <v>1.15603864478166</v>
@@ -866,7 +866,7 @@
         <v>900</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="N3" t="s">
         <v>47</v>
@@ -875,7 +875,7 @@
         <v>48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08136926484062</v>
+        <v>1.06999520481712</v>
       </c>
       <c r="Q3" t="n">
         <v>0.998731607593589</v>
@@ -887,7 +887,7 @@
         <v>4.6166245421767</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="U3" t="n">
         <v>0.9999173464781</v>
@@ -905,16 +905,16 @@
         <v>192</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.29515826773728</v>
+        <v>2.27101733017835</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00048319121426048</v>
+        <v>0.000836690595328864</v>
       </c>
       <c r="AB3" t="n">
         <v>1.13932484045474</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0752279383883071</v>
+        <v>0.0744366757599961</v>
       </c>
       <c r="AD3" t="s">
         <v>47</v>
@@ -923,7 +923,7 @@
         <v>51</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0747621536813002</v>
+        <v>0.0739757902704793</v>
       </c>
       <c r="AG3" t="n">
         <v>0.970695174412968</v>
@@ -935,7 +935,7 @@
         <v>1.55605584008292</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0752279383883071</v>
+        <v>0.0744366757599961</v>
       </c>
       <c r="AK3" t="n">
         <v>0.97052787072339</v>
@@ -944,19 +944,19 @@
         <v>1.56049523863239</v>
       </c>
       <c r="AM3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO3" t="n">
         <v>192</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.29515826773728</v>
+        <v>2.27101733017835</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.00338233849982336</v>
+        <v>0.00215149010227422</v>
       </c>
       <c r="AR3" t="n">
         <v>1.00623022056043</v>
@@ -998,7 +998,7 @@
         <v>600</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="N4" t="s">
         <v>47</v>
@@ -1007,7 +1007,7 @@
         <v>48</v>
       </c>
       <c r="P4" t="n">
-        <v>0.916469315873757</v>
+        <v>0.906185406866212</v>
       </c>
       <c r="Q4" t="n">
         <v>0.998014485619764</v>
@@ -1019,7 +1019,7 @@
         <v>4.23502656211206</v>
       </c>
       <c r="T4" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="U4" t="n">
         <v>0.999860422432155</v>
@@ -1037,16 +1037,16 @@
         <v>166</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.29324895113058</v>
+        <v>2.26751588714622</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00055796811463031</v>
+        <v>0.000965487299879778</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17747149778095</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0331211007475123</v>
+        <v>0.0327494414017846</v>
       </c>
       <c r="AD4" t="s">
         <v>47</v>
@@ -1055,7 +1055,7 @@
         <v>51</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0330522557112562</v>
+        <v>0.0326813688912162</v>
       </c>
       <c r="AG4" t="n">
         <v>0.859726359528916</v>
@@ -1067,7 +1067,7 @@
         <v>1.38250632850401</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0331211007475123</v>
+        <v>0.0327494414017846</v>
       </c>
       <c r="AK4" t="n">
         <v>0.859492457974167</v>
@@ -1076,19 +1076,19 @@
         <v>1.38367415839523</v>
       </c>
       <c r="AM4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO4" t="n">
         <v>166</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.29324895113058</v>
+        <v>2.26751588714622</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00390577680241217</v>
+        <v>0.00248268162826229</v>
       </c>
       <c r="AR4" t="n">
         <v>1.00208291491079</v>
@@ -1132,7 +1132,7 @@
         <v>600</v>
       </c>
       <c r="M5" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="N5" t="s">
         <v>47</v>
@@ -1141,7 +1141,7 @@
         <v>51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28033394326534</v>
+        <v>1.26551960994157</v>
       </c>
       <c r="Q5" t="n">
         <v>0.999791962695814</v>
@@ -1153,7 +1153,7 @@
         <v>0.710998752972665</v>
       </c>
       <c r="T5" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="U5" t="n">
         <v>0.999795764899988</v>
@@ -1171,16 +1171,16 @@
         <v>62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29308790711238</v>
+        <v>2.26655532256648</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00150861046520551</v>
+        <v>0.0026095209305864</v>
       </c>
       <c r="AB5" t="n">
         <v>1.01589978521503</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.347487029392391</v>
+        <v>0.343466368449842</v>
       </c>
       <c r="AD5" t="s">
         <v>47</v>
@@ -1189,7 +1189,7 @@
         <v>51</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.324616519777869</v>
+        <v>0.320860486165164</v>
       </c>
       <c r="AG5" t="n">
         <v>0.99007467292149</v>
@@ -1201,7 +1201,7 @@
         <v>1.25113422504825</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.347487029392391</v>
+        <v>0.343466368449842</v>
       </c>
       <c r="AK5" t="n">
         <v>0.990407805013714</v>
@@ -1210,19 +1210,19 @@
         <v>1.22995859003021</v>
       </c>
       <c r="AM5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO5" t="n">
         <v>62</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.29308790711238</v>
+        <v>2.26655532256648</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0105602732564386</v>
+        <v>0.00671019667865075</v>
       </c>
       <c r="AR5" t="n">
         <v>1.07045393016403</v>
@@ -1260,7 +1260,7 @@
         <v>600</v>
       </c>
       <c r="M6" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="N6" t="s">
         <v>47</v>
@@ -1269,7 +1269,7 @@
         <v>48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.29624180079376</v>
+        <v>1.27853805096221</v>
       </c>
       <c r="Q6" t="n">
         <v>0.999887278397298</v>
@@ -1281,7 +1281,7 @@
         <v>1.003946291558</v>
       </c>
       <c r="T6" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="U6" t="n">
         <v>0.999894443336438</v>
@@ -1299,16 +1299,16 @@
         <v>117</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.29230087312057</v>
+        <v>2.26099319489918</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000793183693121306</v>
+        <v>0.00136911352632303</v>
       </c>
       <c r="AB6" t="n">
         <v>1.0164644481466</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.389685801481711</v>
+        <v>0.384363569211378</v>
       </c>
       <c r="AD6" t="s">
         <v>47</v>
@@ -1317,7 +1317,7 @@
         <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.36323187849675</v>
+        <v>0.358270947361978</v>
       </c>
       <c r="AG6" t="n">
         <v>0.997780915269485</v>
@@ -1329,7 +1329,7 @@
         <v>1.24952730832149</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.389685801481711</v>
+        <v>0.384363569211378</v>
       </c>
       <c r="AK6" t="n">
         <v>0.998122550225431</v>
@@ -1338,7 +1338,7 @@
         <v>1.14932531698564</v>
       </c>
       <c r="AM6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN6" t="s">
         <v>48</v>
@@ -1347,10 +1347,10 @@
         <v>117</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.29230087312057</v>
+        <v>2.26099319489918</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00555228585184914</v>
+        <v>0.00352057763911637</v>
       </c>
       <c r="AR6" t="n">
         <v>1.07282929872356</v>
@@ -1392,7 +1392,7 @@
         <v>300</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="N7" t="s">
         <v>47</v>
@@ -1401,7 +1401,7 @@
         <v>48</v>
       </c>
       <c r="P7" t="n">
-        <v>1.10579702815972</v>
+        <v>1.08694954002875</v>
       </c>
       <c r="Q7" t="n">
         <v>0.997341812842276</v>
@@ -1413,7 +1413,7 @@
         <v>2.44875624758245</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="U7" t="n">
         <v>0.997707251307285</v>
@@ -1431,16 +1431,16 @@
         <v>69</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.29149469066478</v>
+        <v>2.25243786750044</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00135191427177863</v>
+        <v>0.00232552582190311</v>
       </c>
       <c r="AB7" t="n">
         <v>1.07367388439862</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0377788214969031</v>
+        <v>0.0371349095748844</v>
       </c>
       <c r="AD7" t="s">
         <v>47</v>
@@ -1449,7 +1449,7 @@
         <v>51</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0377476994393041</v>
+        <v>0.0371043179696165</v>
       </c>
       <c r="AG7" t="n">
         <v>0.497133148131768</v>
@@ -1461,7 +1461,7 @@
         <v>1.61652391538232</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0377788214969031</v>
+        <v>0.0371349095748844</v>
       </c>
       <c r="AK7" t="n">
         <v>0.496975719496566</v>
@@ -1470,19 +1470,19 @@
         <v>1.61678069534197</v>
       </c>
       <c r="AM7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
         <v>69</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.29149469066478</v>
+        <v>2.25243786750044</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00946339990245041</v>
+        <v>0.00597992354203657</v>
       </c>
       <c r="AR7" t="n">
         <v>1.00082447561206</v>
@@ -1524,7 +1524,7 @@
         <v>300</v>
       </c>
       <c r="M8" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="N8" t="s">
         <v>47</v>
@@ -1533,7 +1533,7 @@
         <v>48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2500716114784</v>
+        <v>1.22747757342384</v>
       </c>
       <c r="Q8" t="n">
         <v>0.999633472356177</v>
@@ -1545,7 +1545,7 @@
         <v>1.1474396140762</v>
       </c>
       <c r="T8" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="U8" t="n">
         <v>0.99977497116895</v>
@@ -1563,16 +1563,16 @@
         <v>77</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.2892168995484</v>
+        <v>2.24784114693663</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00120803002614691</v>
+        <v>0.00207584274783066</v>
       </c>
       <c r="AB8" t="n">
         <v>1.04592823501308</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0452083702163778</v>
+        <v>0.0443912653180071</v>
       </c>
       <c r="AD8" t="s">
         <v>47</v>
@@ -1581,7 +1581,7 @@
         <v>51</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0380952811319747</v>
+        <v>0.037406739592681</v>
       </c>
       <c r="AG8" t="n">
         <v>0.693680686527493</v>
@@ -1593,7 +1593,7 @@
         <v>1.20999491759047</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0452083702163778</v>
+        <v>0.0443912653180071</v>
       </c>
       <c r="AK8" t="n">
         <v>0.695258815852541</v>
@@ -1602,19 +1602,19 @@
         <v>1.20687400068568</v>
       </c>
       <c r="AM8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AN8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO8" t="n">
         <v>77</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.2892168995484</v>
+        <v>2.24784114693663</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00845621018302839</v>
+        <v>0.00533788135156456</v>
       </c>
       <c r="AR8" t="n">
         <v>1.18671837752715</v>
@@ -1654,7 +1654,7 @@
         <v>300</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="N9" t="s">
         <v>47</v>
@@ -1663,7 +1663,7 @@
         <v>48</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07119650180274</v>
+        <v>1.05183548735893</v>
       </c>
       <c r="Q9" t="n">
         <v>0.998592889197321</v>
@@ -1675,7 +1675,7 @@
         <v>1.1975836661462</v>
       </c>
       <c r="T9" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="U9" t="n">
         <v>0.998747896186046</v>
@@ -1693,16 +1693,16 @@
         <v>48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.28895217995805</v>
+        <v>2.24758121193978</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00194804440847494</v>
+        <v>0.00334746137948478</v>
       </c>
       <c r="AB9" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00476396815325628</v>
+        <v>-0.00514805392791875</v>
       </c>
       <c r="AD9" t="s">
         <v>47</v>
@@ -1711,7 +1711,7 @@
         <v>67</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.00396562808995602</v>
+        <v>-0.00389395255460912</v>
       </c>
       <c r="AG9" t="n">
         <v>-0.016477614613488</v>
@@ -1723,13 +1723,13 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.00476396815325628</v>
+        <v>-0.00514805392791875</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.0160211732658191</v>
+        <v>-0.0157938412604248</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.6590185751789</v>
+        <v>1.65883296432331</v>
       </c>
       <c r="AM9" t="s">
         <v>68</v>
@@ -1741,13 +1741,13 @@
         <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.28895217995805</v>
+        <v>2.24758121193978</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0136363108593246</v>
+        <v>0.00860775783296085</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.20131491032209</v>
+        <v>1.32206385561252</v>
       </c>
     </row>
     <row r="10">
@@ -1780,7 +1780,7 @@
         <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="N10" t="s">
         <v>47</v>
@@ -1789,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2386287677836</v>
+        <v>1.21830830268424</v>
       </c>
       <c r="Q10" t="n">
         <v>0.999713524615498</v>
@@ -1801,7 +1801,7 @@
         <v>1.7955954188882</v>
       </c>
       <c r="T10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="U10" t="n">
         <v>0.999884540341955</v>
@@ -1819,16 +1819,16 @@
         <v>70</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.28455849804792</v>
+        <v>2.24707891382181</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.000800195621032545</v>
+        <v>0.00137736886136188</v>
       </c>
       <c r="AB10" t="n">
         <v>1.06371077614318</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00948658459318646</v>
+        <v>0.00933095135088507</v>
       </c>
       <c r="AD10" t="s">
         <v>47</v>
@@ -1837,7 +1837,7 @@
         <v>51</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00949384276810327</v>
+        <v>0.00933809045098793</v>
       </c>
       <c r="AG10" t="n">
         <v>0.030518900730106</v>
@@ -1849,7 +1849,7 @@
         <v>3.79189154513842</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.00948658459318646</v>
+        <v>0.00933095135088507</v>
       </c>
       <c r="AK10" t="n">
         <v>0.0305018423219471</v>
@@ -1867,10 +1867,10 @@
         <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.28455849804792</v>
+        <v>2.24707891382181</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00560136934722782</v>
+        <v>0.00354180564350198</v>
       </c>
       <c r="AR10" t="n">
         <v>0.999235486083549</v>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled.xlsx
@@ -218,10 +218,10 @@
     <t xml:space="preserve">AICc | MDF</t>
   </si>
   <si>
-    <t xml:space="preserve">Noise (LM.MAE) | MDF (LM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noise (HM.MAE) | MDF (HM)</t>
+    <t xml:space="preserve">MDF (LM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDF (HM)</t>
   </si>
   <si>
     <t xml:space="preserve">YMF_Seam</t>
@@ -776,7 +776,7 @@
         <v>2.2761569619547</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00108094292630142</v>
+        <v>0.00337071624206704</v>
       </c>
       <c r="AB2" t="n">
         <v>1.10869208822785</v>
@@ -812,10 +812,10 @@
         <v>1.75863641061905</v>
       </c>
       <c r="AM2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
         <v>149</v>
@@ -824,7 +824,7 @@
         <v>2.2761569619547</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00277956752477507</v>
+        <v>0.00688719318649359</v>
       </c>
       <c r="AR2" t="n">
         <v>1.15603864478166</v>
@@ -899,7 +899,7 @@
         <v>49</v>
       </c>
       <c r="X3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y3" t="n">
         <v>192</v>
@@ -908,7 +908,7 @@
         <v>2.27101733017835</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000836690595328864</v>
+        <v>0.00261222311426031</v>
       </c>
       <c r="AB3" t="n">
         <v>1.13932484045474</v>
@@ -944,10 +944,10 @@
         <v>1.56049523863239</v>
       </c>
       <c r="AM3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO3" t="n">
         <v>192</v>
@@ -956,7 +956,7 @@
         <v>2.27101733017835</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.00215149010227422</v>
+        <v>0.0053374072280561</v>
       </c>
       <c r="AR3" t="n">
         <v>1.00623022056043</v>
@@ -1031,7 +1031,7 @@
         <v>49</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y4" t="n">
         <v>166</v>
@@ -1040,7 +1040,7 @@
         <v>2.26751588714622</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.000965487299879778</v>
+        <v>0.00301237119151321</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17747149778095</v>
@@ -1076,10 +1076,10 @@
         <v>1.38367415839523</v>
       </c>
       <c r="AM4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO4" t="n">
         <v>166</v>
@@ -1088,7 +1088,7 @@
         <v>2.26751588714622</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00248268162826229</v>
+        <v>0.00615500708319985</v>
       </c>
       <c r="AR4" t="n">
         <v>1.00208291491079</v>
@@ -1162,10 +1162,10 @@
         <v>0.704654629061883</v>
       </c>
       <c r="W5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y5" t="n">
         <v>62</v>
@@ -1174,7 +1174,7 @@
         <v>2.26655532256648</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0026095209305864</v>
+        <v>0.00807520956355155</v>
       </c>
       <c r="AB5" t="n">
         <v>1.01589978521503</v>
@@ -1210,10 +1210,10 @@
         <v>1.22995859003021</v>
       </c>
       <c r="AM5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO5" t="n">
         <v>62</v>
@@ -1222,7 +1222,7 @@
         <v>2.26655532256648</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.00671019667865075</v>
+        <v>0.0164996173784996</v>
       </c>
       <c r="AR5" t="n">
         <v>1.07045393016403</v>
@@ -1290,10 +1290,10 @@
         <v>0.971891773133964</v>
       </c>
       <c r="W6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y6" t="n">
         <v>117</v>
@@ -1302,7 +1302,7 @@
         <v>2.26099319489918</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00136911352632303</v>
+        <v>0.00426299148244874</v>
       </c>
       <c r="AB6" t="n">
         <v>1.0164644481466</v>
@@ -1338,7 +1338,7 @@
         <v>1.14932531698564</v>
       </c>
       <c r="AM6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN6" t="s">
         <v>48</v>
@@ -1350,7 +1350,7 @@
         <v>2.26099319489918</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00352057763911637</v>
+        <v>0.00871032854251671</v>
       </c>
       <c r="AR6" t="n">
         <v>1.07282929872356</v>
@@ -1434,7 +1434,7 @@
         <v>2.25243786750044</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00232552582190311</v>
+        <v>0.00720604374639235</v>
       </c>
       <c r="AB7" t="n">
         <v>1.07367388439862</v>
@@ -1470,10 +1470,10 @@
         <v>1.61678069534197</v>
       </c>
       <c r="AM7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO7" t="n">
         <v>69</v>
@@ -1482,7 +1482,7 @@
         <v>2.25243786750044</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00597992354203657</v>
+        <v>0.0147237001953311</v>
       </c>
       <c r="AR7" t="n">
         <v>1.00082447561206</v>
@@ -1554,10 +1554,10 @@
         <v>0.899074238592826</v>
       </c>
       <c r="W8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y8" t="n">
         <v>77</v>
@@ -1566,7 +1566,7 @@
         <v>2.24784114693663</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00207584274783066</v>
+        <v>0.006440284268141</v>
       </c>
       <c r="AB8" t="n">
         <v>1.04592823501308</v>
@@ -1602,10 +1602,10 @@
         <v>1.20687400068568</v>
       </c>
       <c r="AM8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO8" t="n">
         <v>77</v>
@@ -1614,7 +1614,7 @@
         <v>2.24784114693663</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00533788135156456</v>
+        <v>0.0131590673154446</v>
       </c>
       <c r="AR8" t="n">
         <v>1.18671837752715</v>
@@ -1684,10 +1684,10 @@
         <v>1.12969676375376</v>
       </c>
       <c r="W9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y9" t="n">
         <v>48</v>
@@ -1696,13 +1696,13 @@
         <v>2.24758121193978</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00334746137948478</v>
+        <v>0.0103194294544325</v>
       </c>
       <c r="AB9" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00514805392791875</v>
+        <v>-0.00437387748466349</v>
       </c>
       <c r="AD9" t="s">
         <v>47</v>
@@ -1723,13 +1723,13 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.00514805392791875</v>
+        <v>-0.00437387748466349</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.0157938412604248</v>
+        <v>-0.0161857955795053</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.65883296432331</v>
+        <v>1.65915297218831</v>
       </c>
       <c r="AM9" t="s">
         <v>68</v>
@@ -1744,10 +1744,10 @@
         <v>2.24758121193978</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00860775783296085</v>
+        <v>0.0210851045068941</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.32206385561252</v>
+        <v>1.12324878727305</v>
       </c>
     </row>
     <row r="10">
@@ -1813,7 +1813,7 @@
         <v>49</v>
       </c>
       <c r="X10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y10" t="n">
         <v>70</v>
@@ -1822,7 +1822,7 @@
         <v>2.24707891382181</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00137736886136188</v>
+        <v>0.00428833469847012</v>
       </c>
       <c r="AB10" t="n">
         <v>1.06371077614318</v>
@@ -1858,10 +1858,10 @@
         <v>3.7919252851978</v>
       </c>
       <c r="AM10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AN10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO10" t="n">
         <v>70</v>
@@ -1870,7 +1870,7 @@
         <v>2.24707891382181</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.00354180564350198</v>
+        <v>0.00876211089741444</v>
       </c>
       <c r="AR10" t="n">
         <v>0.999235486083549</v>
